--- a/artfynd/A 40169-2026 artfynd.xlsx
+++ b/artfynd/A 40169-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759955</v>
       </c>
       <c r="B2" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40169-2026 artfynd.xlsx
+++ b/artfynd/A 40169-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759955</v>
       </c>
       <c r="B2" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40169-2026 artfynd.xlsx
+++ b/artfynd/A 40169-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759955</v>
       </c>
       <c r="B2" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40169-2026 artfynd.xlsx
+++ b/artfynd/A 40169-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759955</v>
       </c>
       <c r="B2" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40169-2026 artfynd.xlsx
+++ b/artfynd/A 40169-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759955</v>
       </c>
       <c r="B2" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40169-2026 artfynd.xlsx
+++ b/artfynd/A 40169-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759955</v>
       </c>
       <c r="B2" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40169-2026 artfynd.xlsx
+++ b/artfynd/A 40169-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759955</v>
       </c>
       <c r="B2" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40169-2026 artfynd.xlsx
+++ b/artfynd/A 40169-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759955</v>
       </c>
       <c r="B2" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40169-2026 artfynd.xlsx
+++ b/artfynd/A 40169-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759955</v>
       </c>
       <c r="B2" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40169-2026 artfynd.xlsx
+++ b/artfynd/A 40169-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759955</v>
       </c>
       <c r="B2" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40169-2026 artfynd.xlsx
+++ b/artfynd/A 40169-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759955</v>
       </c>
       <c r="B2" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
